--- a/research/traditional_assets/database/data/romania/romania_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_brokerage_investment_banking.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="G2">
-        <v>0.001851851851851852</v>
+        <v>0.001261829652996846</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>4.92</v>
+        <v>-0.028</v>
       </c>
       <c r="L2">
-        <v>0.911111111111111</v>
+        <v>-0.004416403785488959</v>
       </c>
       <c r="M2">
-        <v>0.825</v>
+        <v>2.0722</v>
       </c>
       <c r="N2">
-        <v>0.0378440366972477</v>
+        <v>0.256460396039604</v>
       </c>
       <c r="O2">
-        <v>0.1676829268292683</v>
+        <v>-74.00714285714285</v>
       </c>
       <c r="P2">
-        <v>0.361</v>
+        <v>1.3212</v>
       </c>
       <c r="Q2">
-        <v>0.01655963302752294</v>
+        <v>0.1635148514851485</v>
       </c>
       <c r="R2">
-        <v>0.0733739837398374</v>
+        <v>-47.18571428571429</v>
       </c>
       <c r="S2">
-        <v>0.464</v>
+        <v>0.7509999999999999</v>
       </c>
       <c r="T2">
-        <v>0.5624242424242424</v>
+        <v>0.3624167551394653</v>
       </c>
       <c r="U2">
-        <v>2.48</v>
+        <v>1.6</v>
       </c>
       <c r="V2">
-        <v>0.1137614678899082</v>
+        <v>0.198019801980198</v>
       </c>
       <c r="W2">
-        <v>0.3755725190839695</v>
+        <v>-0.001656804733727811</v>
       </c>
       <c r="X2">
-        <v>0.04509508776585575</v>
+        <v>0.1241421267905118</v>
       </c>
       <c r="Y2">
-        <v>0.3304774313181137</v>
+        <v>-0.1257989315242396</v>
       </c>
       <c r="Z2">
-        <v>0.473186119873817</v>
+        <v>0.3908754623921085</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04464719486967084</v>
+        <v>0.09511363527219981</v>
       </c>
       <c r="AC2">
-        <v>-0.04464719486967084</v>
+        <v>-0.09511363527219981</v>
       </c>
       <c r="AD2">
-        <v>1.8</v>
+        <v>8.91</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.8</v>
+        <v>8.91</v>
       </c>
       <c r="AG2">
-        <v>-0.6799999999999999</v>
+        <v>7.31</v>
       </c>
       <c r="AH2">
-        <v>0.07627118644067796</v>
+        <v>0.5244261330194231</v>
       </c>
       <c r="AI2">
-        <v>0.09</v>
+        <v>0.3506493506493507</v>
       </c>
       <c r="AJ2">
-        <v>-0.03219696969696969</v>
+        <v>0.4749837556855101</v>
       </c>
       <c r="AK2">
-        <v>-0.03881278538812785</v>
+        <v>0.3070138597228055</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.003</v>
+        <v>-0.831</v>
       </c>
       <c r="AQ2">
         <v>-0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="G3">
-        <v>0.001851851851851852</v>
+        <v>0.001261829652996846</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -725,91 +725,91 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>4.92</v>
+        <v>-0.028</v>
       </c>
       <c r="L3">
-        <v>0.911111111111111</v>
+        <v>-0.004416403785488959</v>
       </c>
       <c r="M3">
-        <v>0.825</v>
+        <v>2.0722</v>
       </c>
       <c r="N3">
-        <v>0.0378440366972477</v>
+        <v>0.256460396039604</v>
       </c>
       <c r="O3">
-        <v>0.1676829268292683</v>
+        <v>-74.00714285714285</v>
       </c>
       <c r="P3">
-        <v>0.361</v>
+        <v>1.3212</v>
       </c>
       <c r="Q3">
-        <v>0.01655963302752294</v>
+        <v>0.1635148514851485</v>
       </c>
       <c r="R3">
-        <v>0.0733739837398374</v>
+        <v>-47.18571428571429</v>
       </c>
       <c r="S3">
-        <v>0.464</v>
+        <v>0.7509999999999999</v>
       </c>
       <c r="T3">
-        <v>0.5624242424242424</v>
+        <v>0.3624167551394653</v>
       </c>
       <c r="U3">
-        <v>2.48</v>
+        <v>1.6</v>
       </c>
       <c r="V3">
-        <v>0.1137614678899082</v>
+        <v>0.198019801980198</v>
       </c>
       <c r="W3">
-        <v>0.3755725190839695</v>
+        <v>-0.001656804733727811</v>
       </c>
       <c r="X3">
-        <v>0.04509508776585575</v>
+        <v>0.1241421267905118</v>
       </c>
       <c r="Y3">
-        <v>0.3304774313181137</v>
+        <v>-0.1257989315242396</v>
       </c>
       <c r="Z3">
-        <v>0.473186119873817</v>
+        <v>0.3908754623921085</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04464719486967084</v>
+        <v>0.09511363527219981</v>
       </c>
       <c r="AC3">
-        <v>-0.04464719486967084</v>
+        <v>-0.09511363527219981</v>
       </c>
       <c r="AD3">
-        <v>1.8</v>
+        <v>8.91</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.8</v>
+        <v>8.91</v>
       </c>
       <c r="AG3">
-        <v>-0.6799999999999999</v>
+        <v>7.31</v>
       </c>
       <c r="AH3">
-        <v>0.07627118644067796</v>
+        <v>0.5244261330194231</v>
       </c>
       <c r="AI3">
-        <v>0.09</v>
+        <v>0.3506493506493507</v>
       </c>
       <c r="AJ3">
-        <v>-0.03219696969696969</v>
+        <v>0.4749837556855101</v>
       </c>
       <c r="AK3">
-        <v>-0.03881278538812785</v>
+        <v>0.3070138597228055</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.003</v>
+        <v>-0.831</v>
       </c>
       <c r="AQ3">
         <v>-0</v>

--- a/research/traditional_assets/database/data/romania/romania_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_brokerage_investment_banking.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.2</v>
+        <v>0.053</v>
       </c>
       <c r="G2">
-        <v>0.001261829652996846</v>
+        <v>0.004814814814814814</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -603,91 +603,88 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>-0.028</v>
+        <v>-4.55</v>
       </c>
       <c r="L2">
-        <v>-0.004416403785488959</v>
+        <v>-0.8425925925925926</v>
       </c>
       <c r="M2">
-        <v>2.0722</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.256460396039604</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-74.00714285714285</v>
+        <v>-0</v>
       </c>
       <c r="P2">
-        <v>1.3212</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.1635148514851485</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>-47.18571428571429</v>
+        <v>-0</v>
       </c>
       <c r="S2">
-        <v>0.7509999999999999</v>
-      </c>
-      <c r="T2">
-        <v>0.3624167551394653</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>1.6</v>
+        <v>1.19</v>
       </c>
       <c r="V2">
-        <v>0.198019801980198</v>
+        <v>0.1081818181818182</v>
       </c>
       <c r="W2">
-        <v>-0.001656804733727811</v>
+        <v>-0.3013245033112583</v>
       </c>
       <c r="X2">
-        <v>0.1241421267905118</v>
+        <v>0.0930783333501535</v>
       </c>
       <c r="Y2">
-        <v>-0.1257989315242396</v>
+        <v>-0.3944028366614117</v>
       </c>
       <c r="Z2">
-        <v>0.3908754623921085</v>
+        <v>0.2714932126696833</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.09511363527219981</v>
+        <v>0.07837891692894439</v>
       </c>
       <c r="AC2">
-        <v>-0.09511363527219981</v>
+        <v>-0.07837891692894439</v>
       </c>
       <c r="AD2">
-        <v>8.91</v>
+        <v>10.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>8.91</v>
+        <v>10.4</v>
       </c>
       <c r="AG2">
-        <v>7.31</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.5244261330194231</v>
+        <v>0.485981308411215</v>
       </c>
       <c r="AI2">
-        <v>0.3506493506493507</v>
+        <v>0.4388185654008439</v>
       </c>
       <c r="AJ2">
-        <v>0.4749837556855101</v>
+        <v>0.4557149925779317</v>
       </c>
       <c r="AK2">
-        <v>0.3070138597228055</v>
+        <v>0.4091514882274545</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.831</v>
+        <v>-0.392</v>
       </c>
       <c r="AQ2">
         <v>-0</v>
@@ -710,10 +707,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.2</v>
+        <v>0.053</v>
       </c>
       <c r="G3">
-        <v>0.001261829652996846</v>
+        <v>0.004814814814814814</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -725,91 +722,88 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>-0.028</v>
+        <v>-4.55</v>
       </c>
       <c r="L3">
-        <v>-0.004416403785488959</v>
+        <v>-0.8425925925925926</v>
       </c>
       <c r="M3">
-        <v>2.0722</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.256460396039604</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-74.00714285714285</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>1.3212</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.1635148514851485</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>-47.18571428571429</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>0.7509999999999999</v>
-      </c>
-      <c r="T3">
-        <v>0.3624167551394653</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>1.6</v>
+        <v>1.19</v>
       </c>
       <c r="V3">
-        <v>0.198019801980198</v>
+        <v>0.1081818181818182</v>
       </c>
       <c r="W3">
-        <v>-0.001656804733727811</v>
+        <v>-0.3013245033112583</v>
       </c>
       <c r="X3">
-        <v>0.1241421267905118</v>
+        <v>0.0930783333501535</v>
       </c>
       <c r="Y3">
-        <v>-0.1257989315242396</v>
+        <v>-0.3944028366614117</v>
       </c>
       <c r="Z3">
-        <v>0.3908754623921085</v>
+        <v>0.2714932126696833</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.09511363527219981</v>
+        <v>0.07837891692894439</v>
       </c>
       <c r="AC3">
-        <v>-0.09511363527219981</v>
+        <v>-0.07837891692894439</v>
       </c>
       <c r="AD3">
-        <v>8.91</v>
+        <v>10.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>8.91</v>
+        <v>10.4</v>
       </c>
       <c r="AG3">
-        <v>7.31</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.5244261330194231</v>
+        <v>0.485981308411215</v>
       </c>
       <c r="AI3">
-        <v>0.3506493506493507</v>
+        <v>0.4388185654008439</v>
       </c>
       <c r="AJ3">
-        <v>0.4749837556855101</v>
+        <v>0.4557149925779317</v>
       </c>
       <c r="AK3">
-        <v>0.3070138597228055</v>
+        <v>0.4091514882274545</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.831</v>
+        <v>-0.392</v>
       </c>
       <c r="AQ3">
         <v>-0</v>
